--- a/reviews/a-envoyer/le-loft-2026-08-31.xlsx
+++ b/reviews/a-envoyer/le-loft-2026-08-31.xlsx
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -744,7 +744,7 @@
       <c r="H2" s="10" t="inlineStr"/>
       <c r="I2" s="9" t="inlineStr"/>
     </row>
-    <row r="3" ht="141" customHeight="1">
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>LL-02</t>
@@ -752,30 +752,229 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
+          <t>Mar 01/09</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>voir le visuel</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Story mardi 01/09 — Jour de rentrée, on est ouvert 10h-20h (banque)</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr"/>
+      <c r="I3" s="9" t="inlineStr"/>
+    </row>
+    <row r="4" ht="51" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>LL-03</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Mer 02/09</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>voir le visuel</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Story mercredi 02/09 — JOURNÉE MONDIALE DE LA BARBE : la tienne mérite mieux qu'un coup de tondeuse (banque · renvoi post 18h)</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr"/>
+      <c r="I4" s="9" t="inlineStr"/>
+    </row>
+    <row r="5" ht="201" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>LL-04</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Mer 02/09</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Carrousel (8 visuels)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>voir le visuel</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>La rentrée, ce n'est pas la veille au soir. Ceux qui arrivent le dimanche 6 à 19h en espérant un créneau, on les connaît.
+Cinq points à régler cette semaine. Swipe.
+Le 4 est celui qui change tout : un créneau fixe posé maintenant, et tu ne cours plus après jusqu'à Noël.
+Book ton rdv, lien en bio.
+#rentree #barbierputeaux #coupehomme #ladefense #barbershop #coiffeurhomme</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>LL-05</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Jeu 03/09</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>voir le visuel</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Story jeudi 03/09 — Le dégradé net, c'est une question de transitions (banque)</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>LL-06</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
           <t>Ven 04/09</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>voir le visuel</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Story vendredi 04/09 — Ce que disent nos clients (banque · renvoi post témoignage 18h)</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr"/>
+      <c r="I7" s="9" t="inlineStr"/>
+    </row>
+    <row r="8" ht="141" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>LL-07</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Ven 04/09</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Post</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>IG</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>voir le visuel</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>💬 « Douceur, patience et mise en confiance » — le retour d'une maman après la première coupe de son fils de 2 ans.
 C'est aussi ça le Loft : un endroit où chaque génération se sent bien. Merci pour vos avis, ils nous portent.
@@ -783,12 +982,90 @@
 #avisclients #famille #barbier #puteaux #leloft</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr"/>
-      <c r="I3" s="9" t="inlineStr"/>
+      <c r="H8" s="10" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>LL-08</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Sam 05/09</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>voir le visuel</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Story samedi 05/09 — Samedi, le jour où ça défile. Réserve en avance (banque)</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>LL-09</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Dim 06/09</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>voir le visuel</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Story dimanche 06/09 — Même le dimanche, on t'attend (banque)</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr"/>
+      <c r="I10" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <conditionalFormatting sqref="A2:I3">
+  <conditionalFormatting sqref="A2:I10">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$H2="✅ OK pour publier"</formula>
     </cfRule>
@@ -800,13 +1077,20 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choisir dans la liste" error="Choisissez une des trois décisions du menu, ou laissez la case vide." type="list">
+    <dataValidation sqref="H2:H10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choisir dans la liste" error="Choisissez une des trois décisions du menu, ou laissez la case vide." type="list">
       <formula1>"✅ OK pour publier,✏️ À corriger (voir commentaire),⛔ Ne pas publier"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -818,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,7 +1137,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28T06:09:03</t>
+          <t>2026-08-28T17:14:07</t>
         </is>
       </c>
     </row>
@@ -914,22 +1198,187 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>352462621</v>
+        <v>367688563</v>
       </c>
       <c r="C7" t="n">
         <v>6191921</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2026-09-01T10:00:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Story mardi 01/09 — Jour de rentrée, on est ouvert 10h-20h (banque)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LL-03</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>367688568</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6191921</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-09-02T10:00:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Story mercredi 02/09 — JOURNÉE MONDIALE DE LA BARBE : la tienne mérite mieux qu'un coup de tondeuse (banque · renvoi post 18h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LL-04</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>367696830</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6191921</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-02T18:00:00</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>La rentrée, ce n'est pas la veille au soir. Ceux qui arrivent le dimanche 6 à 19h en espérant un créneau, on les connaît.
+Cinq points à régler cette semaine. Swipe.
+Le 4 est celui qui change tout : un créneau fixe posé maintenant, et tu ne cours plus après jusqu'à Noël.
+Book ton rdv, lien en bio.
+#rentree #barbierputeaux #coupehomme #ladefense #barbershop #coiffeurhomme</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LL-05</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>367688573</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6191921</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-09-03T10:00:00</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Story jeudi 03/09 — Le dégradé net, c'est une question de transitions (banque)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LL-06</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>367688580</v>
+      </c>
+      <c r="C11" t="n">
+        <v>6191921</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-09-04T10:00:00</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Story vendredi 04/09 — Ce que disent nos clients (banque · renvoi post témoignage 18h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LL-07</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>352462621</v>
+      </c>
+      <c r="C12" t="n">
+        <v>6191921</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>2026-09-04T18:00:00</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>💬 « Douceur, patience et mise en confiance » — le retour d'une maman après la première coupe de son fils de 2 ans.
 C'est aussi ça le Loft : un endroit où chaque génération se sent bien. Merci pour vos avis, ils nous portent.
 👇 À ton tour — lien en bio
 #avisclients #famille #barbier #puteaux #leloft</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LL-08</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>367688585</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6191921</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-05T10:00:00</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Story samedi 05/09 — Samedi, le jour où ça défile. Réserve en avance (banque)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LL-09</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>367688592</v>
+      </c>
+      <c r="C14" t="n">
+        <v>6191921</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-09-06T10:00:00</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Story dimanche 06/09 — Même le dimanche, on t'attend (banque)</t>
         </is>
       </c>
     </row>
